--- a/backtest_runs/20260410_193731/by_symbol/BWHL/BWHL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/BWHL/BWHL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-10673.52</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>89326.48</v>
@@ -771,7 +771,7 @@
         <v>-217.3599999999974</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>94800.51999999999</v>
@@ -817,7 +817,7 @@
         <v>-2825.679999999998</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>91974.84</v>
@@ -909,7 +909,7 @@
         <v>-1069.640000000003</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>91654.51999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-715</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>92930.07999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-394.6799999999987</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>92535.39999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-1653.079999999992</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>90882.32000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-1458.59999999999</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>92758.48</v>
@@ -1645,7 +1645,7 @@
         <v>-1430</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>99473.75999999999</v>
